--- a/EKG_Kalite_Yönetim_Sistemi/15_Katmanlı Denetim ve Yetkinlik/01_LPASK1-2 - LPA, Takvim ve Karşı Önlem/EKG-KLT-FRM-44_stok_alani_katmanli_denetim_kontrol_listesi.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/15_Katmanlı Denetim ve Yetkinlik/01_LPASK1-2 - LPA, Takvim ve Karşı Önlem/EKG-KLT-FRM-44_stok_alani_katmanli_denetim_kontrol_listesi.xlsx
@@ -943,7 +943,8 @@
   <pageSetup scale="100"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-KLT-FRM-44&amp;C&amp;"Arial,Regular"&amp;11Stok Alanı Katmanlı Denetim Kontrol Listesi</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 12.06.2026 | Revizyon: 25.09.2026
+Revizyon nedeni: Stok LPA listesi pratik U/UD/NA, nesnel kanıt ve faaliyet odaklı yeniden kuruldu.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -1065,7 +1066,8 @@
   <pageSetup scale="100"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-KLT-FRM-44&amp;C&amp;"Arial,Regular"&amp;11Stok Alanı Katmanlı Denetim Kontrol Listesi</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 12.06.2026 | Revizyon: 25.09.2026
+Revizyon nedeni: Stok LPA listesi pratik U/UD/NA, nesnel kanıt ve faaliyet odaklı yeniden kuruldu.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>